--- a/Deliverables/Interface_Board/BOM/6 Prototypes_Interface_Board.xlsx
+++ b/Deliverables/Interface_Board/BOM/6 Prototypes_Interface_Board.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24931"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25028"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark\ChrisitanRaun-AnnanasMotor\Deliverables\Interface_Board\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\ChristianRaun-EthercatDesign\Deliverables\Interface_Board\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E7F8D6C-AAE5-4173-9E4D-C8243481CBF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE2D612B-6CD1-4E88-9D36-B705E0C032C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="215">
   <si>
     <t>Bill of Material (BOM) for Interface_Board</t>
   </si>
@@ -668,6 +668,26 @@
   </si>
   <si>
     <t>Quantity 6</t>
+  </si>
+  <si>
+    <t>U3*</t>
+  </si>
+  <si>
+    <t>48QFP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMC2130-LA-T
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRINAMIC </t>
+  </si>
+  <si>
+    <t>C915795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QFN-36 Motor Driver ICs ROHS
+</t>
   </si>
 </sst>
 </file>
@@ -1163,7 +1183,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="126">
+  <cellXfs count="128">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1506,6 +1526,9 @@
     <xf numFmtId="164" fontId="13" fillId="6" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1527,9 +1550,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1826,22 +1850,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:30" ht="16.5" thickBot="1">
-      <c r="A1" s="118" t="s">
+      <c r="A1" s="119" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
+      <c r="B1" s="120"/>
+      <c r="C1" s="120"/>
+      <c r="D1" s="120"/>
+      <c r="E1" s="120"/>
+      <c r="F1" s="120"/>
+      <c r="G1" s="120"/>
+      <c r="H1" s="120"/>
+      <c r="I1" s="120"/>
+      <c r="J1" s="120"/>
+      <c r="K1" s="120"/>
+      <c r="L1" s="120"/>
+      <c r="M1" s="120"/>
+      <c r="N1" s="120"/>
     </row>
     <row r="2" spans="1:30" s="1" customFormat="1" ht="16.5" thickBot="1">
       <c r="A2" s="3" t="s">
@@ -1880,7 +1904,7 @@
       <c r="L2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="M2" s="125" t="s">
+      <c r="M2" s="118" t="s">
         <v>208</v>
       </c>
       <c r="N2" s="105" t="s">
@@ -1907,7 +1931,7 @@
       <c r="A3" s="6">
         <v>1</v>
       </c>
-      <c r="B3" s="122" t="s">
+      <c r="B3" s="123" t="s">
         <v>13</v>
       </c>
       <c r="C3" s="50" t="s">
@@ -1952,7 +1976,7 @@
       <c r="A4" s="6">
         <v>2</v>
       </c>
-      <c r="B4" s="123"/>
+      <c r="B4" s="124"/>
       <c r="C4" s="54" t="s">
         <v>23</v>
       </c>
@@ -1995,7 +2019,7 @@
       <c r="A5" s="6">
         <v>3</v>
       </c>
-      <c r="B5" s="123"/>
+      <c r="B5" s="124"/>
       <c r="C5" s="54" t="s">
         <v>30</v>
       </c>
@@ -2038,7 +2062,7 @@
       <c r="A6" s="6">
         <v>4</v>
       </c>
-      <c r="B6" s="123"/>
+      <c r="B6" s="124"/>
       <c r="C6" s="59" t="s">
         <v>37</v>
       </c>
@@ -2081,7 +2105,7 @@
       <c r="A7" s="6">
         <v>5</v>
       </c>
-      <c r="B7" s="123"/>
+      <c r="B7" s="124"/>
       <c r="C7" s="59" t="s">
         <v>44</v>
       </c>
@@ -2124,7 +2148,7 @@
       <c r="A8" s="6">
         <v>6</v>
       </c>
-      <c r="B8" s="123"/>
+      <c r="B8" s="124"/>
       <c r="C8" s="59" t="s">
         <v>51</v>
       </c>
@@ -2167,7 +2191,7 @@
       <c r="A9" s="6">
         <v>7</v>
       </c>
-      <c r="B9" s="123"/>
+      <c r="B9" s="124"/>
       <c r="C9" s="59" t="s">
         <v>58</v>
       </c>
@@ -2211,11 +2235,11 @@
       <c r="A10" s="6">
         <v>8</v>
       </c>
-      <c r="B10" s="123"/>
+      <c r="B10" s="124"/>
       <c r="C10" s="95" t="s">
         <v>189</v>
       </c>
-      <c r="D10" s="94" t="s">
+      <c r="D10" s="126" t="s">
         <v>62</v>
       </c>
       <c r="E10" s="94" t="s">
@@ -2253,7 +2277,7 @@
       <c r="A11" s="6">
         <v>9</v>
       </c>
-      <c r="B11" s="123"/>
+      <c r="B11" s="124"/>
       <c r="C11" s="59" t="s">
         <v>191</v>
       </c>
@@ -2295,7 +2319,7 @@
       <c r="A12" s="6">
         <v>10</v>
       </c>
-      <c r="B12" s="124"/>
+      <c r="B12" s="125"/>
       <c r="C12" s="64" t="s">
         <v>66</v>
       </c>
@@ -2339,7 +2363,7 @@
       <c r="A13" s="6">
         <v>11</v>
       </c>
-      <c r="B13" s="122" t="s">
+      <c r="B13" s="123" t="s">
         <v>73</v>
       </c>
       <c r="C13" s="70" t="s">
@@ -2385,7 +2409,7 @@
       <c r="A14" s="6">
         <v>12</v>
       </c>
-      <c r="B14" s="124"/>
+      <c r="B14" s="125"/>
       <c r="C14" s="64" t="s">
         <v>81</v>
       </c>
@@ -2473,7 +2497,7 @@
     </row>
     <row r="16" spans="1:30" ht="15.75" thickBot="1">
       <c r="A16" s="6"/>
-      <c r="B16" s="122" t="s">
+      <c r="B16" s="123" t="s">
         <v>93</v>
       </c>
       <c r="C16" s="108" t="s">
@@ -2519,7 +2543,7 @@
       <c r="A17" s="6">
         <v>14</v>
       </c>
-      <c r="B17" s="124"/>
+      <c r="B17" s="125"/>
       <c r="C17" s="113" t="s">
         <v>94</v>
       </c>
@@ -2559,7 +2583,7 @@
       <c r="A18" s="6">
         <v>15</v>
       </c>
-      <c r="B18" s="122" t="s">
+      <c r="B18" s="123" t="s">
         <v>99</v>
       </c>
       <c r="C18" s="77" t="s">
@@ -2603,7 +2627,7 @@
     </row>
     <row r="19" spans="1:15" ht="15.75" thickBot="1">
       <c r="A19" s="6"/>
-      <c r="B19" s="123"/>
+      <c r="B19" s="124"/>
       <c r="C19" s="93" t="s">
         <v>193</v>
       </c>
@@ -2643,7 +2667,7 @@
       <c r="A20" s="6">
         <v>16</v>
       </c>
-      <c r="B20" s="123"/>
+      <c r="B20" s="124"/>
       <c r="C20" s="79" t="s">
         <v>106</v>
       </c>
@@ -2687,7 +2711,7 @@
       <c r="A21" s="6">
         <v>17</v>
       </c>
-      <c r="B21" s="123"/>
+      <c r="B21" s="124"/>
       <c r="C21" s="79" t="s">
         <v>111</v>
       </c>
@@ -2731,7 +2755,7 @@
       <c r="A22" s="6">
         <v>18</v>
       </c>
-      <c r="B22" s="123"/>
+      <c r="B22" s="124"/>
       <c r="C22" s="79" t="s">
         <v>116</v>
       </c>
@@ -2775,7 +2799,7 @@
       <c r="A23" s="6">
         <v>19</v>
       </c>
-      <c r="B23" s="123"/>
+      <c r="B23" s="124"/>
       <c r="C23" s="79" t="s">
         <v>123</v>
       </c>
@@ -2819,7 +2843,7 @@
       <c r="A24" s="6">
         <v>20</v>
       </c>
-      <c r="B24" s="123"/>
+      <c r="B24" s="124"/>
       <c r="C24" s="79" t="s">
         <v>130</v>
       </c>
@@ -2863,7 +2887,7 @@
       <c r="A25" s="6">
         <v>21</v>
       </c>
-      <c r="B25" s="124"/>
+      <c r="B25" s="125"/>
       <c r="C25" s="81" t="s">
         <v>136</v>
       </c>
@@ -2907,7 +2931,7 @@
       <c r="A26" s="6">
         <v>22</v>
       </c>
-      <c r="B26" s="122" t="s">
+      <c r="B26" s="123" t="s">
         <v>141</v>
       </c>
       <c r="C26" s="82" t="s">
@@ -2953,7 +2977,7 @@
       <c r="A27" s="6">
         <v>23</v>
       </c>
-      <c r="B27" s="123"/>
+      <c r="B27" s="124"/>
       <c r="C27" s="79" t="s">
         <v>148</v>
       </c>
@@ -2997,7 +3021,7 @@
       <c r="A28" s="6">
         <v>24</v>
       </c>
-      <c r="B28" s="124"/>
+      <c r="B28" s="125"/>
       <c r="C28" s="97" t="s">
         <v>197</v>
       </c>
@@ -3039,7 +3063,7 @@
       <c r="A29" s="6">
         <v>25</v>
       </c>
-      <c r="B29" s="122" t="s">
+      <c r="B29" s="123" t="s">
         <v>156</v>
       </c>
       <c r="C29" s="82" t="s">
@@ -3085,7 +3109,7 @@
       <c r="A30" s="6">
         <v>26</v>
       </c>
-      <c r="B30" s="123"/>
+      <c r="B30" s="124"/>
       <c r="C30" s="85" t="s">
         <v>162</v>
       </c>
@@ -3129,7 +3153,7 @@
       <c r="A31" s="6">
         <v>27</v>
       </c>
-      <c r="B31" s="123"/>
+      <c r="B31" s="124"/>
       <c r="C31" s="85" t="s">
         <v>168</v>
       </c>
@@ -3173,7 +3197,7 @@
       <c r="A32" s="6">
         <v>28</v>
       </c>
-      <c r="B32" s="123"/>
+      <c r="B32" s="124"/>
       <c r="C32" s="26" t="s">
         <v>171</v>
       </c>
@@ -3217,7 +3241,7 @@
       <c r="A33" s="6">
         <v>29</v>
       </c>
-      <c r="B33" s="123"/>
+      <c r="B33" s="124"/>
       <c r="C33" s="79" t="s">
         <v>175</v>
       </c>
@@ -3261,7 +3285,7 @@
       <c r="A34" s="6">
         <v>30</v>
       </c>
-      <c r="B34" s="123"/>
+      <c r="B34" s="124"/>
       <c r="C34" s="89" t="s">
         <v>181</v>
       </c>
@@ -3295,7 +3319,7 @@
       <c r="A35" s="31">
         <v>31</v>
       </c>
-      <c r="B35" s="124"/>
+      <c r="B35" s="125"/>
       <c r="C35" s="91" t="s">
         <v>184</v>
       </c>
@@ -3336,11 +3360,11 @@
       <c r="I36" s="33"/>
       <c r="J36" s="33"/>
       <c r="K36" s="33"/>
-      <c r="L36" s="120" t="s">
+      <c r="L36" s="121" t="s">
         <v>187</v>
       </c>
-      <c r="M36" s="120"/>
-      <c r="N36" s="120"/>
+      <c r="M36" s="121"/>
+      <c r="N36" s="121"/>
       <c r="O36" s="47"/>
     </row>
     <row r="37" spans="1:15" ht="15.75">
@@ -3354,11 +3378,11 @@
       <c r="I37" s="33"/>
       <c r="J37" s="33"/>
       <c r="K37" s="33"/>
-      <c r="L37" s="121" t="s">
+      <c r="L37" s="122" t="s">
         <v>188</v>
       </c>
-      <c r="M37" s="121"/>
-      <c r="N37" s="121"/>
+      <c r="M37" s="122"/>
+      <c r="N37" s="122"/>
       <c r="O37" s="47"/>
     </row>
     <row r="38" spans="1:15">
@@ -3391,6 +3415,30 @@
     </row>
     <row r="45" spans="1:15" ht="15.75" customHeight="1">
       <c r="A45"/>
+      <c r="C45" t="s">
+        <v>214</v>
+      </c>
+      <c r="D45" t="s">
+        <v>209</v>
+      </c>
+      <c r="E45" t="s">
+        <v>210</v>
+      </c>
+      <c r="F45" s="55" t="s">
+        <v>211</v>
+      </c>
+      <c r="G45" t="s">
+        <v>212</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="K45">
+        <v>7</v>
+      </c>
+      <c r="N45" s="127" t="s">
+        <v>22</v>
+      </c>
       <c r="O45" s="47"/>
     </row>
     <row r="46" spans="1:15">
@@ -3594,9 +3642,10 @@
     <hyperlink ref="N19" r:id="rId26" xr:uid="{6B884554-8BB6-4BF7-8096-D834E9729A06}"/>
     <hyperlink ref="N10" r:id="rId27" xr:uid="{44B658D6-BFFD-46B9-B230-29405BAF9534}"/>
     <hyperlink ref="N11" r:id="rId28" xr:uid="{367FEFFE-61E8-47BB-BCCA-FD3358349566}"/>
+    <hyperlink ref="N45" r:id="rId29" xr:uid="{0E7C5907-BF33-4ACE-BFFF-DA9477BCE030}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId29"/>
+  <pageSetup orientation="portrait" r:id="rId30"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
